--- a/reports/gpt2.xlsx
+++ b/reports/gpt2.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-10 00:53:17</t>
+          <t>2026-02-24 21:14:15</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8/30 (26.7%)</t>
+          <t>10/30 (33.3%)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16/81 (19.8%)</t>
+          <t>18/81 (22.2%)</t>
         </is>
       </c>
     </row>
@@ -3499,9 +3499,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4427,9 +4427,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -14371,9 +14371,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B409" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B409" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -16090,9 +16090,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B556" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B556" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
